--- a/public/templates/workers.xlsx
+++ b/public/templates/workers.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -497,15 +497,10 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>הדרכת בטיחות</t>
+          <t>עבודה בגובה</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>עבודה בגובה</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>תוקף דרכון</t>
         </is>
@@ -560,15 +555,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15/03/2027</t>
+          <t>01/09/2027</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>01/09/2027</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>10/2031</t>
         </is>
@@ -621,13 +611,7 @@
           <t>31/01/2027</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>10/04/2027</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>05/2030</t>
         </is>
@@ -682,15 +666,10 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20/02/2027</t>
+          <t>20/02/2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>20/02/2028</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>01/2029</t>
         </is>
@@ -749,11 +728,6 @@
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>01/06/2027</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>07/2032</t>
         </is>
